--- a/tabtools/qa/output/tablex_numfmt_t4.xlsx
+++ b/tabtools/qa/output/tablex_numfmt_t4.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="15" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="30" uniqueCount="13">
   <si>
     <t/>
   </si>
@@ -58,10 +58,270 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
-  <fonts count="62">
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
+  <fonts count="123">
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
     </font>
     <font>
       <sz val="11"/>
@@ -332,7 +592,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="43">
+  <borders count="85">
     <border>
       <left/>
       <right/>
@@ -622,11 +882,293 @@
       <bottom style="thin"/>
       <diagonal style="none"/>
     </border>
+    <border/>
+    <border/>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="43">
+  <cellXfs count="85">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0"/>
@@ -787,6 +1329,168 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="0" fontId="61" fillId="0" borderId="42" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="43" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="44" xfId="0"/>
+    <xf numFmtId="0" fontId="63" fillId="0" borderId="45" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="65" fillId="0" borderId="46" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="67" fillId="0" borderId="47" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="69" fillId="0" borderId="48" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="71" fillId="0" borderId="49" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="73" fillId="0" borderId="50" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="75" fillId="0" borderId="51" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="77" fillId="0" borderId="52" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="79" fillId="0" borderId="53" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="81" fillId="0" borderId="54" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="83" fillId="0" borderId="55" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="85" fillId="0" borderId="56" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="86" fillId="0" borderId="57" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="87" fillId="0" borderId="58" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="88" fillId="0" borderId="59" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="89" fillId="0" borderId="60" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="90" fillId="0" borderId="61" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="91" fillId="0" borderId="62" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="92" fillId="0" borderId="63" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="93" fillId="0" borderId="64" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="94" fillId="0" borderId="65" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="95" fillId="0" borderId="66" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="96" fillId="0" borderId="67" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="97" fillId="0" borderId="68" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="98" fillId="0" borderId="69" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="99" fillId="0" borderId="70" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="100" fillId="0" borderId="71" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="101" fillId="0" borderId="72" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="102" fillId="0" borderId="73" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="103" fillId="0" borderId="74" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="104" fillId="0" borderId="75" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="106" fillId="0" borderId="76" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="108" fillId="0" borderId="77" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="110" fillId="0" borderId="78" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="112" fillId="0" borderId="79" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="114" fillId="0" borderId="80" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="116" fillId="0" borderId="81" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="118" fillId="0" borderId="82" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="120" fillId="0" borderId="83" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="122" fillId="0" borderId="84" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -802,62 +1506,62 @@
   <dimension ref="A1:C5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="12.7109375" style="1" customWidth="true"/>
-    <col min="2" max="3" width="15.7109375" style="2" customWidth="true"/>
+    <col min="1" max="1" width="12.7109375" style="43" customWidth="true"/>
+    <col min="2" max="3" width="15.7109375" style="44" customWidth="true"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="21" t="s">
+      <c r="A1" s="63" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="16" t="s">
+      <c r="B1" s="58" t="s">
         <v>5</v>
       </c>
-      <c r="C1" s="26" t="s">
+      <c r="C1" s="68" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="22" t="s">
+      <c r="A2" s="64" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="19" t="s">
+      <c r="B2" s="61" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="27" t="s">
+      <c r="C2" s="69" t="s">
         <v>0</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="34" t="s">
+      <c r="A3" s="76" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="35">
+      <c r="B3" s="77">
         <v>6072.4230769230771</v>
       </c>
-      <c r="C3" s="36">
+      <c r="C3" s="78">
         <v>19.82692307692308</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="37" t="s">
+      <c r="A4" s="79" t="s">
         <v>3</v>
       </c>
-      <c r="B4" s="38">
+      <c r="B4" s="80">
         <v>6384.681818181818</v>
       </c>
-      <c r="C4" s="39">
+      <c r="C4" s="81">
         <v>24.77272727272727</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="40" t="s">
+      <c r="A5" s="82" t="s">
         <v>4</v>
       </c>
-      <c r="B5" s="41">
+      <c r="B5" s="83">
         <v>6165.2567567567567</v>
       </c>
-      <c r="C5" s="42">
+      <c r="C5" s="84">
         <v>21.297297297297298</v>
       </c>
     </row>
